--- a/excel_data/Super Veo3 Pro - Văn Thế Web V3_3275190461859573671.xlsx
+++ b/excel_data/Super Veo3 Pro - Văn Thế Web V3_3275190461859573671.xlsx
@@ -481,7 +481,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-04-16T09:44:54.926634</t>
+          <t>2026-04-16T10:55:53.047967</t>
         </is>
       </c>
     </row>
@@ -3799,9 +3799,17 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H103" s="2" t="inlineStr"/>
-      <c r="I103" s="2" t="inlineStr"/>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="45" customHeight="1">
       <c r="A104" s="2" t="n">
@@ -3863,7 +3871,11 @@
       </c>
       <c r="G105" s="2" t="inlineStr"/>
       <c r="H105" s="2" t="inlineStr"/>
-      <c r="I105" s="2" t="inlineStr"/>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="45" customHeight="1">
       <c r="A106" s="2" t="n">
@@ -3892,7 +3904,11 @@
       </c>
       <c r="G106" s="2" t="inlineStr"/>
       <c r="H106" s="2" t="inlineStr"/>
-      <c r="I106" s="2" t="inlineStr"/>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="45" customHeight="1">
       <c r="A107" s="2" t="n">
@@ -3919,9 +3935,17 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H107" s="2" t="inlineStr"/>
-      <c r="I107" s="2" t="inlineStr"/>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="45" customHeight="1">
       <c r="A108" s="2" t="n">
@@ -4080,9 +4104,17 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H112" s="2" t="inlineStr"/>
-      <c r="I112" s="2" t="inlineStr"/>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="45" customHeight="1">
       <c r="A113" s="2" t="n">
@@ -4177,7 +4209,11 @@
       </c>
       <c r="G115" s="2" t="inlineStr"/>
       <c r="H115" s="2" t="inlineStr"/>
-      <c r="I115" s="2" t="inlineStr"/>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="116" ht="45" customHeight="1">
       <c r="A116" s="2" t="n">
@@ -4206,7 +4242,11 @@
       </c>
       <c r="G116" s="2" t="inlineStr"/>
       <c r="H116" s="2" t="inlineStr"/>
-      <c r="I116" s="2" t="inlineStr"/>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="45" customHeight="1">
       <c r="A117" s="2" t="n">
@@ -4235,7 +4275,11 @@
       </c>
       <c r="G117" s="2" t="inlineStr"/>
       <c r="H117" s="2" t="inlineStr"/>
-      <c r="I117" s="2" t="inlineStr"/>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="45" customHeight="1">
       <c r="A118" s="2" t="n">
@@ -4264,7 +4308,11 @@
       </c>
       <c r="G118" s="2" t="inlineStr"/>
       <c r="H118" s="2" t="inlineStr"/>
-      <c r="I118" s="2" t="inlineStr"/>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="45" customHeight="1">
       <c r="A119" s="2" t="n">
@@ -4291,9 +4339,17 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H119" s="2" t="inlineStr"/>
-      <c r="I119" s="2" t="inlineStr"/>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="120" ht="45" customHeight="1">
       <c r="A120" s="2" t="n">
@@ -4322,7 +4378,11 @@
       </c>
       <c r="G120" s="2" t="inlineStr"/>
       <c r="H120" s="2" t="inlineStr"/>
-      <c r="I120" s="2" t="inlineStr"/>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="45" customHeight="1">
       <c r="A121" s="2" t="n">
@@ -4349,9 +4409,17 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H121" s="2" t="inlineStr"/>
-      <c r="I121" s="2" t="inlineStr"/>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="45" customHeight="1">
       <c r="A122" s="2" t="n">
@@ -4380,7 +4448,11 @@
       </c>
       <c r="G122" s="2" t="inlineStr"/>
       <c r="H122" s="2" t="inlineStr"/>
-      <c r="I122" s="2" t="inlineStr"/>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="123" ht="45" customHeight="1">
       <c r="A123" s="2" t="n">
@@ -4407,9 +4479,17 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H123" s="2" t="inlineStr"/>
-      <c r="I123" s="2" t="inlineStr"/>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="124" ht="45" customHeight="1">
       <c r="A124" s="2" t="n">
@@ -4438,7 +4518,11 @@
       </c>
       <c r="G124" s="2" t="inlineStr"/>
       <c r="H124" s="2" t="inlineStr"/>
-      <c r="I124" s="2" t="inlineStr"/>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="45" customHeight="1">
       <c r="A125" s="2" t="n">
@@ -4467,7 +4551,11 @@
       </c>
       <c r="G125" s="2" t="inlineStr"/>
       <c r="H125" s="2" t="inlineStr"/>
-      <c r="I125" s="2" t="inlineStr"/>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="45" customHeight="1">
       <c r="A126" s="2" t="n">
@@ -4496,7 +4584,11 @@
       </c>
       <c r="G126" s="2" t="inlineStr"/>
       <c r="H126" s="2" t="inlineStr"/>
-      <c r="I126" s="2" t="inlineStr"/>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="127" ht="45" customHeight="1">
       <c r="A127" s="2" t="n">
@@ -4523,9 +4615,17 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H127" s="2" t="inlineStr"/>
-      <c r="I127" s="2" t="inlineStr"/>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="128" ht="45" customHeight="1">
       <c r="A128" s="2" t="n">
@@ -4552,9 +4652,17 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H128" s="2" t="inlineStr"/>
-      <c r="I128" s="2" t="inlineStr"/>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="45" customHeight="1">
       <c r="A129" s="2" t="n">
@@ -4583,7 +4691,11 @@
       </c>
       <c r="G129" s="2" t="inlineStr"/>
       <c r="H129" s="2" t="inlineStr"/>
-      <c r="I129" s="2" t="inlineStr"/>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="130" ht="45" customHeight="1">
       <c r="A130" s="2" t="n">
@@ -4612,7 +4724,11 @@
       </c>
       <c r="G130" s="2" t="inlineStr"/>
       <c r="H130" s="2" t="inlineStr"/>
-      <c r="I130" s="2" t="inlineStr"/>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="131" ht="45" customHeight="1">
       <c r="A131" s="2" t="n">
@@ -4641,7 +4757,11 @@
       </c>
       <c r="G131" s="2" t="inlineStr"/>
       <c r="H131" s="2" t="inlineStr"/>
-      <c r="I131" s="2" t="inlineStr"/>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="132" ht="45" customHeight="1">
       <c r="A132" s="2" t="n">
@@ -4670,7 +4790,11 @@
       </c>
       <c r="G132" s="2" t="inlineStr"/>
       <c r="H132" s="2" t="inlineStr"/>
-      <c r="I132" s="2" t="inlineStr"/>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="133" ht="45" customHeight="1">
       <c r="A133" s="2" t="n">
@@ -4699,7 +4823,11 @@
       </c>
       <c r="G133" s="2" t="inlineStr"/>
       <c r="H133" s="2" t="inlineStr"/>
-      <c r="I133" s="2" t="inlineStr"/>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="134" ht="45" customHeight="1">
       <c r="A134" s="2" t="n">
@@ -4728,7 +4856,11 @@
       </c>
       <c r="G134" s="2" t="inlineStr"/>
       <c r="H134" s="2" t="inlineStr"/>
-      <c r="I134" s="2" t="inlineStr"/>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="135" ht="45" customHeight="1">
       <c r="A135" s="2" t="n">
@@ -4757,7 +4889,11 @@
       </c>
       <c r="G135" s="2" t="inlineStr"/>
       <c r="H135" s="2" t="inlineStr"/>
-      <c r="I135" s="2" t="inlineStr"/>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="136" ht="45" customHeight="1">
       <c r="A136" s="2" t="n">
@@ -4786,7 +4922,11 @@
       </c>
       <c r="G136" s="2" t="inlineStr"/>
       <c r="H136" s="2" t="inlineStr"/>
-      <c r="I136" s="2" t="inlineStr"/>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="137" ht="45" customHeight="1">
       <c r="A137" s="2" t="n">
@@ -4815,7 +4955,11 @@
       </c>
       <c r="G137" s="2" t="inlineStr"/>
       <c r="H137" s="2" t="inlineStr"/>
-      <c r="I137" s="2" t="inlineStr"/>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="138" ht="45" customHeight="1">
       <c r="A138" s="2" t="n">
@@ -4844,7 +4988,11 @@
       </c>
       <c r="G138" s="2" t="inlineStr"/>
       <c r="H138" s="2" t="inlineStr"/>
-      <c r="I138" s="2" t="inlineStr"/>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="139" ht="45" customHeight="1">
       <c r="A139" s="2" t="n">
@@ -4873,7 +5021,11 @@
       </c>
       <c r="G139" s="2" t="inlineStr"/>
       <c r="H139" s="2" t="inlineStr"/>
-      <c r="I139" s="2" t="inlineStr"/>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="140" ht="45" customHeight="1">
       <c r="A140" s="2" t="n">
@@ -4902,7 +5054,11 @@
       </c>
       <c r="G140" s="2" t="inlineStr"/>
       <c r="H140" s="2" t="inlineStr"/>
-      <c r="I140" s="2" t="inlineStr"/>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="141" ht="45" customHeight="1">
       <c r="A141" s="2" t="n">
@@ -4931,7 +5087,11 @@
       </c>
       <c r="G141" s="2" t="inlineStr"/>
       <c r="H141" s="2" t="inlineStr"/>
-      <c r="I141" s="2" t="inlineStr"/>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="142" ht="45" customHeight="1">
       <c r="A142" s="2" t="n">
@@ -4960,7 +5120,11 @@
       </c>
       <c r="G142" s="2" t="inlineStr"/>
       <c r="H142" s="2" t="inlineStr"/>
-      <c r="I142" s="2" t="inlineStr"/>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="143" ht="45" customHeight="1">
       <c r="A143" s="2" t="n">
@@ -4987,9 +5151,17 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr"/>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H143" s="2" t="inlineStr"/>
-      <c r="I143" s="2" t="inlineStr"/>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="144" ht="45" customHeight="1">
       <c r="A144" s="2" t="n">
@@ -5018,7 +5190,11 @@
       </c>
       <c r="G144" s="2" t="inlineStr"/>
       <c r="H144" s="2" t="inlineStr"/>
-      <c r="I144" s="2" t="inlineStr"/>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="145" ht="45" customHeight="1">
       <c r="A145" s="2" t="n">
@@ -5047,7 +5223,11 @@
       </c>
       <c r="G145" s="2" t="inlineStr"/>
       <c r="H145" s="2" t="inlineStr"/>
-      <c r="I145" s="2" t="inlineStr"/>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="146" ht="45" customHeight="1">
       <c r="A146" s="2" t="n">
@@ -5074,9 +5254,17 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr"/>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H146" s="2" t="inlineStr"/>
-      <c r="I146" s="2" t="inlineStr"/>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="147" ht="45" customHeight="1">
       <c r="A147" s="2" t="n">
@@ -5103,9 +5291,17 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr"/>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H147" s="2" t="inlineStr"/>
-      <c r="I147" s="2" t="inlineStr"/>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="148" ht="45" customHeight="1">
       <c r="A148" s="2" t="n">
@@ -5134,7 +5330,11 @@
       </c>
       <c r="G148" s="2" t="inlineStr"/>
       <c r="H148" s="2" t="inlineStr"/>
-      <c r="I148" s="2" t="inlineStr"/>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="149" ht="45" customHeight="1">
       <c r="A149" s="2" t="n">
@@ -5161,9 +5361,17 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr"/>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H149" s="2" t="inlineStr"/>
-      <c r="I149" s="2" t="inlineStr"/>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="150" ht="45" customHeight="1">
       <c r="A150" s="2" t="n">
@@ -5190,9 +5398,17 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr"/>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H150" s="2" t="inlineStr"/>
-      <c r="I150" s="2" t="inlineStr"/>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="151" ht="45" customHeight="1">
       <c r="A151" s="2" t="n">
@@ -5221,7 +5437,11 @@
       </c>
       <c r="G151" s="2" t="inlineStr"/>
       <c r="H151" s="2" t="inlineStr"/>
-      <c r="I151" s="2" t="inlineStr"/>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="152" ht="45" customHeight="1">
       <c r="A152" s="2" t="n">
@@ -5250,7 +5470,11 @@
       </c>
       <c r="G152" s="2" t="inlineStr"/>
       <c r="H152" s="2" t="inlineStr"/>
-      <c r="I152" s="2" t="inlineStr"/>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="153" ht="45" customHeight="1">
       <c r="A153" s="2" t="n">
@@ -5279,7 +5503,11 @@
       </c>
       <c r="G153" s="2" t="inlineStr"/>
       <c r="H153" s="2" t="inlineStr"/>
-      <c r="I153" s="2" t="inlineStr"/>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="154" ht="45" customHeight="1">
       <c r="A154" s="2" t="n">
@@ -5308,7 +5536,11 @@
       </c>
       <c r="G154" s="2" t="inlineStr"/>
       <c r="H154" s="2" t="inlineStr"/>
-      <c r="I154" s="2" t="inlineStr"/>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="155" ht="45" customHeight="1">
       <c r="A155" s="2" t="n">
@@ -5337,7 +5569,11 @@
       </c>
       <c r="G155" s="2" t="inlineStr"/>
       <c r="H155" s="2" t="inlineStr"/>
-      <c r="I155" s="2" t="inlineStr"/>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="156" ht="45" customHeight="1">
       <c r="A156" s="2" t="n">
@@ -5366,7 +5602,11 @@
       </c>
       <c r="G156" s="2" t="inlineStr"/>
       <c r="H156" s="2" t="inlineStr"/>
-      <c r="I156" s="2" t="inlineStr"/>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="157" ht="45" customHeight="1">
       <c r="A157" s="2" t="n">
@@ -5395,7 +5635,11 @@
       </c>
       <c r="G157" s="2" t="inlineStr"/>
       <c r="H157" s="2" t="inlineStr"/>
-      <c r="I157" s="2" t="inlineStr"/>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="158" ht="45" customHeight="1">
       <c r="A158" s="2" t="n">
@@ -5424,7 +5668,11 @@
       </c>
       <c r="G158" s="2" t="inlineStr"/>
       <c r="H158" s="2" t="inlineStr"/>
-      <c r="I158" s="2" t="inlineStr"/>
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="159" ht="45" customHeight="1">
       <c r="A159" s="2" t="n">
@@ -5453,7 +5701,11 @@
       </c>
       <c r="G159" s="2" t="inlineStr"/>
       <c r="H159" s="2" t="inlineStr"/>
-      <c r="I159" s="2" t="inlineStr"/>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="160" ht="45" customHeight="1">
       <c r="A160" s="2" t="n">
@@ -5482,7 +5734,11 @@
       </c>
       <c r="G160" s="2" t="inlineStr"/>
       <c r="H160" s="2" t="inlineStr"/>
-      <c r="I160" s="2" t="inlineStr"/>
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="161" ht="45" customHeight="1">
       <c r="A161" s="2" t="n">
@@ -5511,7 +5767,11 @@
       </c>
       <c r="G161" s="2" t="inlineStr"/>
       <c r="H161" s="2" t="inlineStr"/>
-      <c r="I161" s="2" t="inlineStr"/>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="162" ht="45" customHeight="1">
       <c r="A162" s="2" t="n">
@@ -5540,7 +5800,11 @@
       </c>
       <c r="G162" s="2" t="inlineStr"/>
       <c r="H162" s="2" t="inlineStr"/>
-      <c r="I162" s="2" t="inlineStr"/>
+      <c r="I162" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="163" ht="45" customHeight="1">
       <c r="A163" s="2" t="n">
@@ -5569,7 +5833,11 @@
       </c>
       <c r="G163" s="2" t="inlineStr"/>
       <c r="H163" s="2" t="inlineStr"/>
-      <c r="I163" s="2" t="inlineStr"/>
+      <c r="I163" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="164" ht="45" customHeight="1">
       <c r="A164" s="2" t="n">
@@ -5598,7 +5866,11 @@
       </c>
       <c r="G164" s="2" t="inlineStr"/>
       <c r="H164" s="2" t="inlineStr"/>
-      <c r="I164" s="2" t="inlineStr"/>
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="165" ht="45" customHeight="1">
       <c r="A165" s="2" t="n">
@@ -5627,7 +5899,11 @@
       </c>
       <c r="G165" s="2" t="inlineStr"/>
       <c r="H165" s="2" t="inlineStr"/>
-      <c r="I165" s="2" t="inlineStr"/>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="166" ht="45" customHeight="1">
       <c r="A166" s="2" t="n">
@@ -5656,7 +5932,11 @@
       </c>
       <c r="G166" s="2" t="inlineStr"/>
       <c r="H166" s="2" t="inlineStr"/>
-      <c r="I166" s="2" t="inlineStr"/>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="167" ht="45" customHeight="1">
       <c r="A167" s="2" t="n">
@@ -5685,7 +5965,11 @@
       </c>
       <c r="G167" s="2" t="inlineStr"/>
       <c r="H167" s="2" t="inlineStr"/>
-      <c r="I167" s="2" t="inlineStr"/>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="168" ht="45" customHeight="1">
       <c r="A168" s="2" t="n">

--- a/excel_data/Super Veo3 Pro - Văn Thế Web V3_3275190461859573671.xlsx
+++ b/excel_data/Super Veo3 Pro - Văn Thế Web V3_3275190461859573671.xlsx
@@ -481,7 +481,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-04-16T10:55:53.047967</t>
+          <t>2026-04-17T14:24:39.443089</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,11 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
           <t>v</t>
@@ -796,7 +800,11 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H12" s="2" t="inlineStr"/>
       <c r="I12" s="2" t="inlineStr">
         <is>
@@ -829,7 +837,11 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H13" s="2" t="inlineStr"/>
       <c r="I13" s="2" t="inlineStr">
         <is>
@@ -862,7 +874,11 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr">
         <is>
@@ -895,7 +911,11 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H15" s="2" t="inlineStr"/>
       <c r="I15" s="2" t="inlineStr">
         <is>
@@ -928,7 +948,11 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="inlineStr">
         <is>
@@ -961,7 +985,11 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H17" s="2" t="inlineStr"/>
       <c r="I17" s="2" t="inlineStr">
         <is>
@@ -994,7 +1022,11 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H18" s="2" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr">
         <is>
@@ -1027,7 +1059,11 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H19" s="2" t="inlineStr"/>
       <c r="I19" s="2" t="inlineStr">
         <is>
@@ -1060,7 +1096,11 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr">
         <is>
@@ -1093,7 +1133,11 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H21" s="2" t="inlineStr"/>
       <c r="I21" s="2" t="inlineStr">
         <is>
@@ -1192,7 +1236,11 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H24" s="2" t="inlineStr"/>
       <c r="I24" s="2" t="inlineStr">
         <is>
@@ -1225,7 +1273,11 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H25" s="2" t="inlineStr"/>
       <c r="I25" s="2" t="inlineStr">
         <is>
@@ -1291,7 +1343,11 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H27" s="2" t="inlineStr"/>
       <c r="I27" s="2" t="inlineStr">
         <is>
@@ -1357,7 +1413,11 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H29" s="2" t="inlineStr"/>
       <c r="I29" s="2" t="inlineStr">
         <is>
@@ -1390,7 +1450,11 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H30" s="2" t="inlineStr"/>
       <c r="I30" s="2" t="inlineStr">
         <is>
@@ -1423,7 +1487,11 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H31" s="2" t="inlineStr"/>
       <c r="I31" s="2" t="inlineStr">
         <is>
@@ -1456,7 +1524,11 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr">
         <is>
@@ -1489,7 +1561,11 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H33" s="2" t="inlineStr"/>
       <c r="I33" s="2" t="inlineStr">
         <is>
@@ -1522,7 +1598,11 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H34" s="2" t="inlineStr"/>
       <c r="I34" s="2" t="inlineStr">
         <is>
@@ -1555,7 +1635,11 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H35" s="2" t="inlineStr"/>
       <c r="I35" s="2" t="inlineStr">
         <is>
@@ -1588,7 +1672,11 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H36" s="2" t="inlineStr"/>
       <c r="I36" s="2" t="inlineStr">
         <is>
@@ -1621,7 +1709,11 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H37" s="2" t="inlineStr"/>
       <c r="I37" s="2" t="inlineStr">
         <is>
@@ -1654,7 +1746,11 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H38" s="2" t="inlineStr"/>
       <c r="I38" s="2" t="inlineStr">
         <is>
@@ -1687,7 +1783,11 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H39" s="2" t="inlineStr"/>
       <c r="I39" s="2" t="inlineStr">
         <is>
@@ -1753,7 +1853,11 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H41" s="2" t="inlineStr"/>
       <c r="I41" s="2" t="inlineStr">
         <is>
@@ -1819,7 +1923,11 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H43" s="2" t="inlineStr"/>
       <c r="I43" s="2" t="inlineStr">
         <is>
@@ -1852,7 +1960,11 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H44" s="2" t="inlineStr"/>
       <c r="I44" s="2" t="inlineStr">
         <is>
@@ -1918,7 +2030,11 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H46" s="2" t="inlineStr"/>
       <c r="I46" s="2" t="inlineStr">
         <is>
@@ -1951,7 +2067,11 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H47" s="2" t="inlineStr"/>
       <c r="I47" s="2" t="inlineStr">
         <is>
@@ -1984,7 +2104,11 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H48" s="2" t="inlineStr"/>
       <c r="I48" s="2" t="inlineStr">
         <is>
@@ -2017,7 +2141,11 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H49" s="2" t="inlineStr"/>
       <c r="I49" s="2" t="inlineStr">
         <is>
@@ -2050,7 +2178,11 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H50" s="2" t="inlineStr"/>
       <c r="I50" s="2" t="inlineStr">
         <is>
@@ -2116,7 +2248,11 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H52" s="2" t="inlineStr"/>
       <c r="I52" s="2" t="inlineStr">
         <is>
@@ -2149,7 +2285,11 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H53" s="2" t="inlineStr"/>
       <c r="I53" s="2" t="inlineStr">
         <is>
@@ -2182,7 +2322,11 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H54" s="2" t="inlineStr"/>
       <c r="I54" s="2" t="inlineStr">
         <is>
@@ -2215,7 +2359,11 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H55" s="2" t="inlineStr"/>
       <c r="I55" s="2" t="inlineStr">
         <is>
